--- a/DOCS/Meeting Preps/Meeting Prep Apr 6/Incorporate123_Packages.xlsx
+++ b/DOCS/Meeting Preps/Meeting Prep Apr 6/Incorporate123_Packages.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexo\Projects\inc123\DOCS\Meeting Prep Apr 6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexo\Projects\inc123\DOCS\Meeting Preps\Meeting Prep Apr 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F38DAB1-3299-49B2-8CE6-15330BDD8D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C0555D-14BD-46C6-BB5D-E905121819DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Current Packages" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="124">
   <si>
     <t>Current Package Lineup — Feature Comparison</t>
   </si>
@@ -241,9 +241,6 @@
     <t>FORMATION — Included in All Tiers</t>
   </si>
   <si>
-    <t>TBD</t>
-  </si>
-  <si>
     <t>COMPLIANCE — Included in All Tiers</t>
   </si>
   <si>
@@ -253,15 +250,9 @@
     <t>Virtual Office Address</t>
   </si>
   <si>
-    <t>Corporate Seal</t>
-  </si>
-  <si>
     <t>PRIVACY — Gold Only</t>
   </si>
   <si>
-    <t>TBD = Items pending confirmation. All other features are confirmed.</t>
-  </si>
-  <si>
     <t>Key Changes: Current → Proposed</t>
   </si>
   <si>
@@ -371,13 +362,59 @@
   </si>
   <si>
     <t>8 packages</t>
+  </si>
+  <si>
+    <t>Nevada Executive VO add-on $300</t>
+  </si>
+  <si>
+    <t>privacy service addon</t>
+  </si>
+  <si>
+    <t>Executive VO Upgrade</t>
+  </si>
+  <si>
+    <t>Privacy Services Upgrade</t>
+  </si>
+  <si>
+    <t>CA or FL State Registration Fees CA or FL Registered Agent Fees</t>
+  </si>
+  <si>
+    <t>CA or FL State Registration Fees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
+  </si>
+  <si>
+    <t>CA or FL Registered Agent Fees</t>
+  </si>
+  <si>
+    <t>Bank Account Opening Document Package</t>
+  </si>
+  <si>
+    <t>Gorvernment Filing Services Add-ons</t>
+  </si>
+  <si>
+    <t>Initial state filings and fees</t>
+  </si>
+  <si>
+    <t>Year-Round Nominee Director / Manager</t>
+  </si>
+  <si>
+    <t>Foreign State Filing (all 50 states)</t>
+  </si>
+  <si>
+    <t>Domestication Filing (WY or NV)</t>
+  </si>
+  <si>
+    <t>Part-time Private Suite Upgrade</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -447,13 +484,78 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1E3A5F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FFE65100"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -478,11 +580,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF8E1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3E0"/>
       </patternFill>
     </fill>
     <fill>
@@ -518,7 +615,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -550,23 +647,59 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -870,52 +1003,60 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="16" width="14" customWidth="1"/>
+    <col min="2" max="4" width="14" customWidth="1"/>
+    <col min="5" max="6" width="14" style="24" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="9" width="14" style="24" customWidth="1"/>
+    <col min="10" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="14" style="24" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="14" style="24" customWidth="1"/>
+    <col min="15" max="16" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -924,25 +1065,25 @@
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="21" t="s">
         <v>4</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="21" t="s">
         <v>7</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="21" t="s">
         <v>10</v>
       </c>
       <c r="J4" s="2" t="s">
@@ -951,13 +1092,13 @@
       <c r="K4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="21" t="s">
         <v>13</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="21" t="s">
         <v>15</v>
       </c>
       <c r="O4" s="2" t="s">
@@ -974,25 +1115,25 @@
       <c r="B5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="22" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="22" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="22" t="s">
         <v>19</v>
       </c>
       <c r="J5" s="3" t="s">
@@ -1001,13 +1142,13 @@
       <c r="K5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="L5" s="22" t="s">
         <v>20</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="N5" s="22" t="s">
         <v>20</v>
       </c>
       <c r="O5" s="3" t="s">
@@ -1024,25 +1165,25 @@
       <c r="B6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="23" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="23" t="s">
         <v>27</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="23" t="s">
         <v>29</v>
       </c>
       <c r="J6" s="4" t="s">
@@ -1051,13 +1192,13 @@
       <c r="K6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="L6" s="23" t="s">
         <v>27</v>
       </c>
       <c r="M6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="N6" s="23" t="s">
         <v>29</v>
       </c>
       <c r="O6" s="4" t="s">
@@ -1066,24 +1207,27 @@
       <c r="P6" s="4" t="s">
         <v>28</v>
       </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="C7" s="24"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
+      <c r="C8" s="25"/>
       <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
       <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="25"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
+      <c r="L8" s="25"/>
       <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
+      <c r="N8" s="25"/>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
     </row>
@@ -1094,25 +1238,25 @@
       <c r="B9" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="26" t="s">
         <v>32</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="7" t="s">
+      <c r="E9" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="26" t="s">
         <v>32</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="7" t="s">
+      <c r="H9" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="26" t="s">
         <v>32</v>
       </c>
       <c r="J9" s="7" t="s">
@@ -1121,13 +1265,13 @@
       <c r="K9" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="L9" s="26" t="s">
         <v>32</v>
       </c>
       <c r="M9" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="N9" s="7" t="s">
+      <c r="N9" s="26" t="s">
         <v>32</v>
       </c>
       <c r="O9" s="7" t="s">
@@ -1144,25 +1288,25 @@
       <c r="B10" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="26" t="s">
         <v>32</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="7" t="s">
+      <c r="E10" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="26" t="s">
         <v>32</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="7" t="s">
+      <c r="H10" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="26" t="s">
         <v>32</v>
       </c>
       <c r="J10" s="7" t="s">
@@ -1171,13 +1315,13 @@
       <c r="K10" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="L10" s="26" t="s">
         <v>32</v>
       </c>
       <c r="M10" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="N10" s="7" t="s">
+      <c r="N10" s="26" t="s">
         <v>32</v>
       </c>
       <c r="O10" s="7" t="s">
@@ -1194,25 +1338,25 @@
       <c r="B11" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="26" t="s">
         <v>32</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="7" t="s">
+      <c r="E11" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="26" t="s">
         <v>32</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="7" t="s">
+      <c r="H11" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="26" t="s">
         <v>32</v>
       </c>
       <c r="J11" s="7" t="s">
@@ -1221,13 +1365,13 @@
       <c r="K11" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L11" s="7" t="s">
+      <c r="L11" s="26" t="s">
         <v>32</v>
       </c>
       <c r="M11" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="N11" s="7" t="s">
+      <c r="N11" s="26" t="s">
         <v>32</v>
       </c>
       <c r="O11" s="7" t="s">
@@ -1244,25 +1388,25 @@
       <c r="B12" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="26" t="s">
         <v>32</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="7" t="s">
+      <c r="E12" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="26" t="s">
         <v>32</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="7" t="s">
+      <c r="H12" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="26" t="s">
         <v>32</v>
       </c>
       <c r="J12" s="8" t="s">
@@ -1271,13 +1415,13 @@
       <c r="K12" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="L12" s="8" t="s">
+      <c r="L12" s="28" t="s">
         <v>36</v>
       </c>
       <c r="M12" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="N12" s="8" t="s">
+      <c r="N12" s="28" t="s">
         <v>36</v>
       </c>
       <c r="O12" s="8" t="s">
@@ -1294,25 +1438,25 @@
       <c r="B13" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="27" t="s">
         <v>38</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="27" t="s">
         <v>38</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="27" t="s">
         <v>38</v>
       </c>
       <c r="J13" s="9" t="s">
@@ -1321,13 +1465,13 @@
       <c r="K13" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="L13" s="9" t="s">
+      <c r="L13" s="27" t="s">
         <v>38</v>
       </c>
       <c r="M13" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="N13" s="9" t="s">
+      <c r="N13" s="27" t="s">
         <v>38</v>
       </c>
       <c r="O13" s="9" t="s">
@@ -1344,25 +1488,25 @@
       <c r="B14" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="26" t="s">
         <v>32</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="7" t="s">
+      <c r="E14" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="26" t="s">
         <v>32</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="7" t="s">
+      <c r="H14" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="26" t="s">
         <v>32</v>
       </c>
       <c r="J14" s="7" t="s">
@@ -1371,13 +1515,13 @@
       <c r="K14" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L14" s="7" t="s">
+      <c r="L14" s="26" t="s">
         <v>32</v>
       </c>
       <c r="M14" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="N14" s="7" t="s">
+      <c r="N14" s="26" t="s">
         <v>32</v>
       </c>
       <c r="O14" s="7" t="s">
@@ -1394,25 +1538,25 @@
       <c r="B15" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="28" t="s">
         <v>36</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="27" t="s">
         <v>38</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="I15" s="27" t="s">
         <v>38</v>
       </c>
       <c r="J15" s="9" t="s">
@@ -1421,13 +1565,13 @@
       <c r="K15" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="L15" s="9" t="s">
+      <c r="L15" s="27" t="s">
         <v>38</v>
       </c>
       <c r="M15" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="N15" s="9" t="s">
+      <c r="N15" s="27" t="s">
         <v>38</v>
       </c>
       <c r="O15" s="9" t="s">
@@ -1436,24 +1580,27 @@
       <c r="P15" s="9" t="s">
         <v>38</v>
       </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="C16" s="24"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
+      <c r="C17" s="25"/>
       <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
       <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
+      <c r="L17" s="25"/>
       <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
+      <c r="N17" s="25"/>
       <c r="O17" s="5"/>
       <c r="P17" s="5"/>
     </row>
@@ -1464,25 +1611,25 @@
       <c r="B18" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="26" t="s">
         <v>32</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" s="7" t="s">
+      <c r="E18" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="26" t="s">
         <v>32</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H18" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="7" t="s">
+      <c r="H18" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="26" t="s">
         <v>32</v>
       </c>
       <c r="J18" s="7" t="s">
@@ -1491,13 +1638,13 @@
       <c r="K18" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L18" s="7" t="s">
+      <c r="L18" s="26" t="s">
         <v>32</v>
       </c>
       <c r="M18" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="N18" s="7" t="s">
+      <c r="N18" s="26" t="s">
         <v>32</v>
       </c>
       <c r="O18" s="7" t="s">
@@ -1514,25 +1661,25 @@
       <c r="B19" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="26" t="s">
         <v>32</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" s="7" t="s">
+      <c r="E19" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" s="26" t="s">
         <v>32</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H19" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="7" t="s">
+      <c r="H19" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="26" t="s">
         <v>32</v>
       </c>
       <c r="J19" s="7" t="s">
@@ -1541,13 +1688,13 @@
       <c r="K19" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L19" s="7" t="s">
+      <c r="L19" s="26" t="s">
         <v>32</v>
       </c>
       <c r="M19" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="N19" s="7" t="s">
+      <c r="N19" s="26" t="s">
         <v>32</v>
       </c>
       <c r="O19" s="7" t="s">
@@ -1564,25 +1711,25 @@
       <c r="B20" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="26" t="s">
         <v>32</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F20" s="7" t="s">
+      <c r="E20" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" s="26" t="s">
         <v>32</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H20" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="7" t="s">
+      <c r="H20" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="26" t="s">
         <v>32</v>
       </c>
       <c r="J20" s="7" t="s">
@@ -1591,13 +1738,13 @@
       <c r="K20" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L20" s="7" t="s">
+      <c r="L20" s="26" t="s">
         <v>32</v>
       </c>
       <c r="M20" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="N20" s="7" t="s">
+      <c r="N20" s="26" t="s">
         <v>32</v>
       </c>
       <c r="O20" s="7" t="s">
@@ -1606,24 +1753,27 @@
       <c r="P20" s="7" t="s">
         <v>32</v>
       </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="C21" s="24"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
+      <c r="C22" s="25"/>
       <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
       <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
+      <c r="L22" s="25"/>
       <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
+      <c r="N22" s="25"/>
       <c r="O22" s="5"/>
       <c r="P22" s="5"/>
     </row>
@@ -1634,40 +1784,40 @@
       <c r="B23" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="28" t="s">
         <v>36</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E23" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F23" s="8" t="s">
+      <c r="E23" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23" s="28" t="s">
         <v>36</v>
       </c>
       <c r="G23" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H23" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I23" s="8" t="s">
+      <c r="H23" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="I23" s="28" t="s">
         <v>36</v>
       </c>
       <c r="J23" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K23" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="L23" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="M23" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="N23" s="7" t="s">
+      <c r="K23" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L23" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="N23" s="26" t="s">
         <v>32</v>
       </c>
       <c r="O23" s="8" t="s">
@@ -1684,25 +1834,25 @@
       <c r="B24" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="28" t="s">
         <v>36</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="8" t="s">
+      <c r="E24" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="28" t="s">
         <v>36</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="H24" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" s="8" t="s">
+      <c r="H24" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="28" t="s">
         <v>36</v>
       </c>
       <c r="J24" s="8" t="s">
@@ -1711,13 +1861,13 @@
       <c r="K24" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="L24" s="8" t="s">
+      <c r="L24" s="28" t="s">
         <v>36</v>
       </c>
       <c r="M24" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="N24" s="8" t="s">
+      <c r="N24" s="28" t="s">
         <v>36</v>
       </c>
       <c r="O24" s="8" t="s">
@@ -1734,25 +1884,25 @@
       <c r="B25" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="28" t="s">
         <v>36</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E25" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F25" s="7" t="s">
+      <c r="E25" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="F25" s="26" t="s">
         <v>32</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="H25" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I25" s="7" t="s">
+      <c r="H25" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="I25" s="26" t="s">
         <v>32</v>
       </c>
       <c r="J25" s="8" t="s">
@@ -1761,13 +1911,13 @@
       <c r="K25" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="L25" s="8" t="s">
+      <c r="L25" s="28" t="s">
         <v>36</v>
       </c>
       <c r="M25" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="N25" s="8" t="s">
+      <c r="N25" s="28" t="s">
         <v>36</v>
       </c>
       <c r="O25" s="8" t="s">
@@ -1784,25 +1934,25 @@
       <c r="B26" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="28" t="s">
         <v>36</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E26" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F26" s="7" t="s">
+      <c r="E26" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="F26" s="26" t="s">
         <v>32</v>
       </c>
       <c r="G26" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H26" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="7" t="s">
+      <c r="H26" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="26" t="s">
         <v>32</v>
       </c>
       <c r="J26" s="8" t="s">
@@ -1811,13 +1961,13 @@
       <c r="K26" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L26" s="7" t="s">
+      <c r="L26" s="26" t="s">
         <v>32</v>
       </c>
       <c r="M26" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="N26" s="7" t="s">
+      <c r="N26" s="26" t="s">
         <v>32</v>
       </c>
       <c r="O26" s="7" t="s">
@@ -1826,24 +1976,27 @@
       <c r="P26" s="7" t="s">
         <v>32</v>
       </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="C27" s="24"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>50</v>
       </c>
       <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
+      <c r="C28" s="24"/>
       <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
       <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
+      <c r="L28" s="25"/>
       <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
+      <c r="N28" s="25"/>
       <c r="O28" s="5"/>
       <c r="P28" s="5"/>
     </row>
@@ -1854,25 +2007,25 @@
       <c r="B29" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="26" t="s">
         <v>32</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E29" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F29" s="8" t="s">
+      <c r="E29" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="F29" s="28" t="s">
         <v>36</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H29" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" s="7" t="s">
+      <c r="H29" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" s="26" t="s">
         <v>32</v>
       </c>
       <c r="J29" s="8" t="s">
@@ -1881,13 +2034,13 @@
       <c r="K29" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="L29" s="8" t="s">
+      <c r="L29" s="28" t="s">
         <v>36</v>
       </c>
       <c r="M29" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="N29" s="7" t="s">
+      <c r="N29" s="26" t="s">
         <v>32</v>
       </c>
       <c r="O29" s="7" t="s">
@@ -1904,25 +2057,25 @@
       <c r="B30" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="26" t="s">
         <v>32</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E30" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F30" s="8" t="s">
+      <c r="E30" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="F30" s="28" t="s">
         <v>36</v>
       </c>
       <c r="G30" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H30" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I30" s="7" t="s">
+      <c r="H30" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I30" s="26" t="s">
         <v>32</v>
       </c>
       <c r="J30" s="8" t="s">
@@ -1931,13 +2084,13 @@
       <c r="K30" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="L30" s="8" t="s">
+      <c r="L30" s="28" t="s">
         <v>36</v>
       </c>
       <c r="M30" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="N30" s="7" t="s">
+      <c r="N30" s="26" t="s">
         <v>32</v>
       </c>
       <c r="O30" s="7" t="s">
@@ -1954,25 +2107,25 @@
       <c r="B31" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="26" t="s">
         <v>32</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E31" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F31" s="8" t="s">
+      <c r="E31" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="F31" s="28" t="s">
         <v>36</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H31" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="7" t="s">
+      <c r="H31" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I31" s="26" t="s">
         <v>32</v>
       </c>
       <c r="J31" s="7" t="s">
@@ -1981,13 +2134,13 @@
       <c r="K31" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L31" s="7" t="s">
+      <c r="L31" s="26" t="s">
         <v>32</v>
       </c>
       <c r="M31" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="N31" s="7" t="s">
+      <c r="N31" s="26" t="s">
         <v>32</v>
       </c>
       <c r="O31" s="7" t="s">
@@ -2010,19 +2163,19 @@
       <c r="D32" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E32" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F32" s="8" t="s">
+      <c r="E32" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="F32" s="28" t="s">
         <v>36</v>
       </c>
       <c r="G32" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="H32" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I32" s="8" t="s">
+      <c r="H32" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="I32" s="28" t="s">
         <v>36</v>
       </c>
       <c r="J32" s="7" t="s">
@@ -2031,13 +2184,13 @@
       <c r="K32" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L32" s="7" t="s">
+      <c r="L32" s="26" t="s">
         <v>32</v>
       </c>
       <c r="M32" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="N32" s="7" t="s">
+      <c r="N32" s="26" t="s">
         <v>32</v>
       </c>
       <c r="O32" s="7" t="s">
@@ -2054,16 +2207,16 @@
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
       <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
-      <c r="L34" s="5"/>
+      <c r="L34" s="25"/>
       <c r="M34" s="5"/>
-      <c r="N34" s="5"/>
+      <c r="N34" s="25"/>
       <c r="O34" s="5"/>
       <c r="P34" s="5"/>
     </row>
@@ -2080,19 +2233,19 @@
       <c r="D35" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E35" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F35" s="8" t="s">
+      <c r="E35" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="F35" s="28" t="s">
         <v>36</v>
       </c>
       <c r="G35" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="H35" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I35" s="8" t="s">
+      <c r="H35" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="I35" s="28" t="s">
         <v>36</v>
       </c>
       <c r="J35" s="8" t="s">
@@ -2101,13 +2254,13 @@
       <c r="K35" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="L35" s="8" t="s">
+      <c r="L35" s="28" t="s">
         <v>36</v>
       </c>
       <c r="M35" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="N35" s="8" t="s">
+      <c r="N35" s="28" t="s">
         <v>36</v>
       </c>
       <c r="O35" s="7" t="s">
@@ -2124,16 +2277,16 @@
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
       <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="25"/>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
+      <c r="L37" s="25"/>
       <c r="M37" s="5"/>
-      <c r="N37" s="5"/>
+      <c r="N37" s="25"/>
       <c r="O37" s="5"/>
       <c r="P37" s="5"/>
     </row>
@@ -2150,19 +2303,19 @@
       <c r="D38" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="E38" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F38" s="10" t="s">
+      <c r="E38" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="F38" s="29" t="s">
         <v>59</v>
       </c>
       <c r="G38" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="H38" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="I38" s="10" t="s">
+      <c r="H38" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="I38" s="29" t="s">
         <v>59</v>
       </c>
       <c r="J38" s="10" t="s">
@@ -2171,13 +2324,13 @@
       <c r="K38" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="L38" s="10" t="s">
+      <c r="L38" s="29" t="s">
         <v>59</v>
       </c>
       <c r="M38" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="N38" s="10" t="s">
+      <c r="N38" s="29" t="s">
         <v>59</v>
       </c>
       <c r="O38" s="10" t="s">
@@ -2200,19 +2353,19 @@
       <c r="D39" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="E39" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F39" s="10" t="s">
+      <c r="E39" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="F39" s="29" t="s">
         <v>59</v>
       </c>
       <c r="G39" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="H39" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="I39" s="10" t="s">
+      <c r="H39" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="I39" s="29" t="s">
         <v>59</v>
       </c>
       <c r="J39" s="10" t="s">
@@ -2221,13 +2374,13 @@
       <c r="K39" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="L39" s="10" t="s">
+      <c r="L39" s="29" t="s">
         <v>59</v>
       </c>
       <c r="M39" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="N39" s="10" t="s">
+      <c r="N39" s="29" t="s">
         <v>59</v>
       </c>
       <c r="O39" s="10" t="s">
@@ -2250,19 +2403,19 @@
       <c r="D40" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="E40" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F40" s="10" t="s">
+      <c r="E40" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="F40" s="29" t="s">
         <v>59</v>
       </c>
       <c r="G40" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="H40" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="I40" s="10" t="s">
+      <c r="H40" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="I40" s="29" t="s">
         <v>59</v>
       </c>
       <c r="J40" s="10" t="s">
@@ -2271,13 +2424,13 @@
       <c r="K40" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="L40" s="10" t="s">
+      <c r="L40" s="29" t="s">
         <v>59</v>
       </c>
       <c r="M40" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="N40" s="10" t="s">
+      <c r="N40" s="29" t="s">
         <v>59</v>
       </c>
       <c r="O40" s="10" t="s">
@@ -2285,6 +2438,21 @@
       </c>
       <c r="P40" s="10" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="26" x14ac:dyDescent="0.35">
+      <c r="C41" s="20" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="25" x14ac:dyDescent="0.35">
+      <c r="C42" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="25" x14ac:dyDescent="0.35">
+      <c r="C43" s="6" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2298,7 +2466,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -2306,43 +2474,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.4">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
@@ -2475,7 +2643,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>32</v>
@@ -2503,17 +2671,17 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>32</v>
+      <c r="A12" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>32</v>
@@ -2524,22 +2692,22 @@
       <c r="G12" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>32</v>
+      <c r="H12" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>36</v>
@@ -2550,119 +2718,119 @@
       <c r="F13" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>36</v>
+      <c r="G13" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A15" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+      <c r="A17" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="26" x14ac:dyDescent="0.35">
-      <c r="A18" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>32</v>
@@ -2691,7 +2859,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>32</v>
@@ -2718,169 +2886,170 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="26" x14ac:dyDescent="0.35">
-      <c r="A23" s="5" t="s">
+    <row r="21" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="22" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+      <c r="A22" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
+      <c r="B23" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A26" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="7" t="s">
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+    </row>
+    <row r="27" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A27" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A28" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
+      <c r="A28" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>36</v>
+      <c r="C29" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F29" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>36</v>
+      <c r="F29" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>32</v>
@@ -2889,122 +3058,117 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A30" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A31" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A33" s="5" t="s">
+      <c r="A31" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A34" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A36" s="5" t="s">
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A33" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A34" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A35" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A36" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>59</v>
@@ -3030,10 +3194,13 @@
       <c r="I37" s="10" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A38" s="6" t="s">
-        <v>60</v>
+      <c r="N37" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A38" s="31" t="s">
+        <v>122</v>
       </c>
       <c r="B38" s="10" t="s">
         <v>59</v>
@@ -3060,56 +3227,42 @@
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A39" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F39" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="G39" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="I39" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A42" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="15"/>
-      <c r="H42" s="15"/>
-      <c r="I42" s="15"/>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="E39" s="19"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A43" s="32" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A44" s="18" t="s">
+        <v>113</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A42:I42"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3124,142 +3277,142 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.4">
-      <c r="A1" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
+      <c r="A1" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="B5" s="12" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="12" t="s">
+      <c r="C5" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="13" t="s">
+    </row>
+    <row r="6" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B6" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C6" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="12" t="s">
+    <row r="7" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B7" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C7" s="12" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="13" t="s">
+    <row r="8" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B8" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C8" s="11" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="12" t="s">
+    <row r="9" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B9" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C9" s="12" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="13" t="s">
+    <row r="10" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B10" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C10" s="11" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="12" t="s">
+    <row r="11" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B11" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C11" s="12" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="13" t="s">
+    <row r="12" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B12" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C12" s="11" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="12" t="s">
+    <row r="13" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B13" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C13" s="12" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="13" t="s">
+    <row r="14" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B14" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C14" s="11" t="s">
         <v>106</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>109</v>
       </c>
     </row>
   </sheetData>
